--- a/SGC-CKN/Excel/27f744b3-6af0-47c4-8d59-ef22df2da1d0_Thanh_Hoá_P1-109_D800_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/27f744b3-6af0-47c4-8d59-ef22df2da1d0_Thanh_Hoá_P1-109_D800_05-04-2026.xlsx
@@ -1165,7 +1165,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.56</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.16</v>
@@ -1174,10 +1174,10 @@
         <v>0.52</v>
       </c>
       <c r="I11" s="5">
-        <v>0.6</v>
+        <v>1.16</v>
       </c>
       <c r="J11" s="8">
-        <v>1.16</v>
+        <v>2.25</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1343,16 +1343,16 @@
         <v>-21.56</v>
       </c>
       <c r="G16" s="23">
-        <v>-25.84</v>
+        <v>-25.56</v>
       </c>
       <c r="H16" s="23">
         <v>0.67</v>
       </c>
       <c r="I16" s="23">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="J16" s="19">
-        <v>6.42</v>
+        <v>6</v>
       </c>
       <c r="K16" s="24" t="s">
         <v>30</v>
@@ -1375,7 +1375,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="26">
-        <v>-25.84</v>
+        <v>-25.56</v>
       </c>
       <c r="G17" s="26">
         <v>-40.3</v>
@@ -1384,10 +1384,10 @@
         <v>0.42</v>
       </c>
       <c r="I17" s="26">
-        <v>14.46</v>
+        <v>14.74</v>
       </c>
       <c r="J17" s="19">
-        <v>34.7</v>
+        <v>35.38</v>
       </c>
       <c r="K17" s="27" t="s">
         <v>49</v>
@@ -1577,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.56</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.16</v>
@@ -1586,10 +1586,10 @@
         <v>0.52</v>
       </c>
       <c r="H2" s="5">
-        <v>0.6</v>
+        <v>1.16</v>
       </c>
       <c r="I2" s="8">
-        <v>1.16</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1725,16 +1725,16 @@
         <v>-21.56</v>
       </c>
       <c r="F7" s="23">
-        <v>-25.84</v>
+        <v>-25.56</v>
       </c>
       <c r="G7" s="23">
         <v>0.67</v>
       </c>
       <c r="H7" s="23">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="I7" s="19">
-        <v>6.42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1751,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="26">
-        <v>-25.84</v>
+        <v>-25.56</v>
       </c>
       <c r="F8" s="26">
         <v>-40.3</v>
@@ -1760,10 +1760,10 @@
         <v>0.42</v>
       </c>
       <c r="H8" s="26">
-        <v>14.46</v>
+        <v>14.74</v>
       </c>
       <c r="I8" s="19">
-        <v>34.7</v>
+        <v>35.38</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1809,7 +1809,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="34">
-        <v>-0.56</v>
+        <v>0</v>
       </c>
       <c r="F10" s="34">
         <v>-44.39</v>
@@ -1818,10 +1818,10 @@
         <v>13.2</v>
       </c>
       <c r="H10" s="34">
-        <v>43.83</v>
+        <v>44.39</v>
       </c>
       <c r="I10" s="34">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>
